--- a/data/Diessenhofen/investment_decision/Diessenhofen_MFH_until_2004_investment_decision.xlsx
+++ b/data/Diessenhofen/investment_decision/Diessenhofen_MFH_until_2004_investment_decision.xlsx
@@ -470,22 +470,22 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>scen_all_invested_available_unit</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>655.4498604769423</v>
+        <v>467.4127104116985</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -508,19 +508,19 @@
         <v>394656.8380198025</v>
       </c>
       <c r="F2" t="n">
-        <v>689.1114891758189</v>
+        <v>470.1381713021154</v>
       </c>
       <c r="G2" t="n">
         <v>394656.8380198025</v>
       </c>
       <c r="H2" t="n">
-        <v>688.6691911304472</v>
+        <v>471.3324823282755</v>
       </c>
       <c r="I2" t="n">
         <v>394656.8380198025</v>
       </c>
       <c r="J2" t="n">
-        <v>677.7421327491671</v>
+        <v>455.9691564878294</v>
       </c>
       <c r="K2" t="n">
         <v>394656.8380198025</v>
@@ -531,7 +531,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>928.6912558933333</v>
+        <v>515.5526491105285</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -545,19 +545,19 @@
         <v>394656.8380198025</v>
       </c>
       <c r="F3" t="n">
-        <v>932.3160511503037</v>
+        <v>538.3062669782132</v>
       </c>
       <c r="G3" t="n">
         <v>394656.8380198025</v>
       </c>
       <c r="H3" t="n">
-        <v>965.8301111585855</v>
+        <v>471.3324823282755</v>
       </c>
       <c r="I3" t="n">
         <v>394656.8380198025</v>
       </c>
       <c r="J3" t="n">
-        <v>954.3713701431933</v>
+        <v>455.9691564878294</v>
       </c>
       <c r="K3" t="n">
         <v>394656.8380198025</v>
@@ -568,7 +568,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>1174.800554324045</v>
+        <v>957.7731531648465</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -582,19 +582,19 @@
         <v>394656.8380198025</v>
       </c>
       <c r="F4" t="n">
-        <v>1174.809508780715</v>
+        <v>960.281983688858</v>
       </c>
       <c r="G4" t="n">
         <v>394656.8380198025</v>
       </c>
       <c r="H4" t="n">
-        <v>1176.807260967981</v>
+        <v>932.6978617505732</v>
       </c>
       <c r="I4" t="n">
         <v>394656.8380198025</v>
       </c>
       <c r="J4" t="n">
-        <v>1176.807260967981</v>
+        <v>932.6978617505735</v>
       </c>
       <c r="K4" t="n">
         <v>394656.8380198025</v>
@@ -605,7 +605,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>1224.267497213733</v>
+        <v>1590.2781774072</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -619,19 +619,19 @@
         <v>394656.8380198025</v>
       </c>
       <c r="F5" t="n">
-        <v>1228.414451899382</v>
+        <v>1592.332349195661</v>
       </c>
       <c r="G5" t="n">
         <v>394656.8380198025</v>
       </c>
       <c r="H5" t="n">
-        <v>1249.205355770965</v>
+        <v>1592.354839067796</v>
       </c>
       <c r="I5" t="n">
         <v>394656.8380198025</v>
       </c>
       <c r="J5" t="n">
-        <v>1249.205355770965</v>
+        <v>1592.420243761602</v>
       </c>
       <c r="K5" t="n">
         <v>394656.8380198025</v>
@@ -642,7 +642,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>1224.267497213733</v>
+        <v>1590.2781774072</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -656,19 +656,19 @@
         <v>394656.8380198025</v>
       </c>
       <c r="F6" t="n">
-        <v>1228.414451899382</v>
+        <v>1592.332349195661</v>
       </c>
       <c r="G6" t="n">
         <v>394656.8380198025</v>
       </c>
       <c r="H6" t="n">
-        <v>1249.205355770965</v>
+        <v>1592.354839067796</v>
       </c>
       <c r="I6" t="n">
         <v>394656.8380198025</v>
       </c>
       <c r="J6" t="n">
-        <v>1249.205355770965</v>
+        <v>1592.420243761602</v>
       </c>
       <c r="K6" t="n">
         <v>394656.8380198025</v>
@@ -683,32 +683,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Diessenhofen_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Diessenhofen_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>591.9852570297037</v>
+        <v>699.1126853932584</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>591.9852570297037</v>
+        <v>699.1126853932584</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>345.6615493695562</v>
+        <v>408.2135005007723</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>345.6615493695562</v>
+        <v>408.2135005007723</v>
       </c>
     </row>
     <row r="8">
@@ -720,32 +720,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Diessenhofen_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Diessenhofen_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>591.9852570297037</v>
+        <v>699.1126853932584</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>591.9852570297037</v>
+        <v>699.1126853932584</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>458.7846777450956</v>
+        <v>541.8077296130378</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>458.7846777450956</v>
+        <v>541.8077296130378</v>
       </c>
     </row>
     <row r="9">
@@ -757,32 +757,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Diessenhofen_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Diessenhofen_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>591.9852570297037</v>
+        <v>699.1126853932584</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>591.9852570297037</v>
+        <v>699.1126853932584</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>508.1840196872331</v>
+        <v>600.1465246957247</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>508.1840196872331</v>
+        <v>600.1465246957247</v>
       </c>
     </row>
     <row r="10">
@@ -794,32 +794,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Diessenhofen_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Diessenhofen_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>591.9852570297037</v>
+        <v>699.1126853932584</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>591.9852570297037</v>
+        <v>699.1126853932584</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>533.8599973047922</v>
+        <v>630.4689042637149</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>533.8599973047922</v>
+        <v>630.4689042637149</v>
       </c>
     </row>
     <row r="11">
@@ -831,32 +831,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Diessenhofen_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Diessenhofen_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>591.9852570297037</v>
+        <v>699.1126853932584</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>591.9852570297037</v>
+        <v>699.1126853932584</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>548.8318962091188</v>
+        <v>648.1501629169434</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>548.8318962091188</v>
+        <v>648.1501629169434</v>
       </c>
     </row>
     <row r="12">
@@ -864,7 +864,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.1167315304847059</v>
+        <v>0.1029832850070588</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -878,19 +878,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1167315304847059</v>
+        <v>0.1053009362734042</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1167315304847059</v>
+        <v>0.1065809626164706</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1167315304847059</v>
+        <v>0.1065809626164706</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -901,7 +901,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1167315304847059</v>
+        <v>0.1065809626164706</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -915,19 +915,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1167315304847059</v>
+        <v>0.1065809626164706</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1174703336470588</v>
+        <v>0.1065809626164706</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1174703336470588</v>
+        <v>0.1065809626164706</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -938,7 +938,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1218068144188235</v>
+        <v>0.1080891240457631</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -952,19 +952,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1218068144188235</v>
+        <v>0.109262889075224</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1218068144188235</v>
+        <v>0.1065809626164706</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1218068144188235</v>
+        <v>0.1065809626164706</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -975,7 +975,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.1286894244611861</v>
+        <v>0.1080891240457631</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -989,19 +989,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1292599763611172</v>
+        <v>0.109262889075224</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1313432751705538</v>
+        <v>0.1065809626164706</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1311185335281686</v>
+        <v>0.1065809626164706</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1012,7 +1012,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1286894244611861</v>
+        <v>0.1080891240457631</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1026,19 +1026,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1292599763611172</v>
+        <v>0.109262889075224</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1313432751705538</v>
+        <v>0.1065809626164706</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1311185335281686</v>
+        <v>0.1065809626164706</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1049,7 +1049,7 @@
         <v>46023</v>
       </c>
       <c r="B17" t="n">
-        <v>1.267078435992663</v>
+        <v>3.944479259056001</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1063,19 +1063,19 @@
         <v>18.1187636448</v>
       </c>
       <c r="F17" t="n">
-        <v>1.246060312976698</v>
+        <v>3.931738097999999</v>
       </c>
       <c r="G17" t="n">
         <v>18.1187636448</v>
       </c>
       <c r="H17" t="n">
-        <v>1.078497835999997</v>
+        <v>3.931738097999999</v>
       </c>
       <c r="I17" t="n">
         <v>18.1187636448</v>
       </c>
       <c r="J17" t="n">
-        <v>1.117546784458292</v>
+        <v>3.931738097999999</v>
       </c>
       <c r="K17" t="n">
         <v>18.1187636448</v>
@@ -1086,7 +1086,7 @@
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>1.267078435992663</v>
+        <v>5.082773503699082</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1100,19 +1100,19 @@
         <v>18.1187636448</v>
       </c>
       <c r="F18" t="n">
-        <v>1.246060312976698</v>
+        <v>5.094208410215423</v>
       </c>
       <c r="G18" t="n">
         <v>18.1187636448</v>
       </c>
       <c r="H18" t="n">
-        <v>1.078497835999997</v>
+        <v>5.061580134909812</v>
       </c>
       <c r="I18" t="n">
         <v>18.1187636448</v>
       </c>
       <c r="J18" t="n">
-        <v>1.117546784458292</v>
+        <v>5.061580134909811</v>
       </c>
       <c r="K18" t="n">
         <v>18.1187636448</v>
@@ -1123,7 +1123,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>1.267078435992663</v>
+        <v>5.082773503699082</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1137,19 +1137,19 @@
         <v>18.1187636448</v>
       </c>
       <c r="F19" t="n">
-        <v>1.246060312976698</v>
+        <v>5.094208410215423</v>
       </c>
       <c r="G19" t="n">
         <v>18.1187636448</v>
       </c>
       <c r="H19" t="n">
-        <v>1.078497835999997</v>
+        <v>5.061580134909812</v>
       </c>
       <c r="I19" t="n">
         <v>18.1187636448</v>
       </c>
       <c r="J19" t="n">
-        <v>1.117546784458292</v>
+        <v>5.061580134909811</v>
       </c>
       <c r="K19" t="n">
         <v>18.1187636448</v>
@@ -1160,7 +1160,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.8864694369989721</v>
+        <v>3.562002871690489</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1174,19 +1174,19 @@
         <v>18.1187636448</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8258482976313014</v>
+        <v>3.682417574434331</v>
       </c>
       <c r="G20" t="n">
         <v>18.1187636448</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6044977991286599</v>
+        <v>2.771760746353301</v>
       </c>
       <c r="I20" t="n">
         <v>18.1187636448</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6283765986320853</v>
+        <v>2.771623903678417</v>
       </c>
       <c r="K20" t="n">
         <v>18.1187636448</v>
@@ -1197,7 +1197,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.8864694369989721</v>
+        <v>3.235889454069393</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1211,19 +1211,19 @@
         <v>18.1187636448</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8258482976313014</v>
+        <v>3.235493508</v>
       </c>
       <c r="G21" t="n">
         <v>18.1187636448</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6044977991286599</v>
+        <v>2.570203689002773</v>
       </c>
       <c r="I21" t="n">
         <v>18.1187636448</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6283765986320853</v>
+        <v>2.552289836149773</v>
       </c>
       <c r="K21" t="n">
         <v>18.1187636448</v>
@@ -1493,7 +1493,7 @@
         <v>49675</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.2721342375211305</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1507,19 +1507,19 @@
         <v>18.1187636448</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.2542942317574469</v>
       </c>
       <c r="G29" t="n">
         <v>18.1187636448</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.5392489179999987</v>
       </c>
       <c r="I29" t="n">
         <v>18.1187636448</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.5392489180000001</v>
       </c>
       <c r="K29" t="n">
         <v>18.1187636448</v>
@@ -1530,7 +1530,7 @@
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.3790067661376689</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1544,19 +1544,19 @@
         <v>18.1187636448</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.2542942317574469</v>
       </c>
       <c r="G30" t="n">
         <v>18.1187636448</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1.078497835999999</v>
       </c>
       <c r="I30" t="n">
         <v>18.1187636448</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1.078497835999999</v>
       </c>
       <c r="K30" t="n">
         <v>18.1187636448</v>
@@ -1567,7 +1567,7 @@
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.5392489180000001</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1581,19 +1581,19 @@
         <v>18.1187636448</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.5392489180000001</v>
       </c>
       <c r="G31" t="n">
         <v>18.1187636448</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1.078497835999999</v>
       </c>
       <c r="I31" t="n">
         <v>18.1187636448</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1.078497835999999</v>
       </c>
       <c r="K31" t="n">
         <v>18.1187636448</v>
@@ -2142,13 +2142,13 @@
         <v>53.87266966157533</v>
       </c>
       <c r="H46" t="n">
-        <v>49.04007155825366</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>48.50185252820037</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>49.04007155825366</v>
       </c>
       <c r="K46" t="n">
         <v>48.50185252820037</v>
@@ -2344,7 +2344,7 @@
         <v>46023</v>
       </c>
       <c r="B52" t="n">
-        <v>24.47857157225403</v>
+        <v>23.19134584327139</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2358,19 +2358,19 @@
         <v>117.5424354444279</v>
       </c>
       <c r="F52" t="n">
-        <v>24.05115822872805</v>
+        <v>23.13039033337624</v>
       </c>
       <c r="G52" t="n">
         <v>117.5424354444279</v>
       </c>
       <c r="H52" t="n">
-        <v>23.57673548410697</v>
+        <v>22.07714345213011</v>
       </c>
       <c r="I52" t="n">
         <v>39.44125092820288</v>
       </c>
       <c r="J52" t="n">
-        <v>23.83482762797797</v>
+        <v>23.10848659473028</v>
       </c>
       <c r="K52" t="n">
         <v>39.44125092820288</v>
@@ -2381,7 +2381,7 @@
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>26.19440293568377</v>
+        <v>26.71051733351407</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2395,19 +2395,19 @@
         <v>117.5424354444279</v>
       </c>
       <c r="F53" t="n">
-        <v>25.91113684447265</v>
+        <v>26.49598060488874</v>
       </c>
       <c r="G53" t="n">
         <v>117.5424354444279</v>
       </c>
       <c r="H53" t="n">
-        <v>25.75403968818383</v>
+        <v>25.37920366136118</v>
       </c>
       <c r="I53" t="n">
         <v>59.55868959980688</v>
       </c>
       <c r="J53" t="n">
-        <v>26.07737699569348</v>
+        <v>25.62709402283277</v>
       </c>
       <c r="K53" t="n">
         <v>59.55868959980688</v>
@@ -2418,7 +2418,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>31.46642884995561</v>
+        <v>31.33440734742684</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2432,19 +2432,19 @@
         <v>117.5424354444279</v>
       </c>
       <c r="F54" t="n">
-        <v>31.41840249715048</v>
+        <v>31.31161512055252</v>
       </c>
       <c r="G54" t="n">
         <v>117.5424354444279</v>
       </c>
       <c r="H54" t="n">
-        <v>31.41809024974224</v>
+        <v>30.28534344312463</v>
       </c>
       <c r="I54" t="n">
         <v>71.24902794151585</v>
       </c>
       <c r="J54" t="n">
-        <v>31.41809024974224</v>
+        <v>31.31459608192566</v>
       </c>
       <c r="K54" t="n">
         <v>71.24902794151585</v>
@@ -2455,7 +2455,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>30.83723183973919</v>
+        <v>30.71647339022352</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2469,19 +2469,19 @@
         <v>117.5424354444279</v>
       </c>
       <c r="F55" t="n">
-        <v>30.69404709741498</v>
+        <v>30.71080459469528</v>
       </c>
       <c r="G55" t="n">
         <v>117.5424354444279</v>
       </c>
       <c r="H55" t="n">
-        <v>30.70596466779226</v>
+        <v>30.72375718089002</v>
       </c>
       <c r="I55" t="n">
         <v>78.70776229687482</v>
       </c>
       <c r="J55" t="n">
-        <v>30.70818542055574</v>
+        <v>30.72375718089002</v>
       </c>
       <c r="K55" t="n">
         <v>78.70776229687482</v>
@@ -2492,7 +2492,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>30.69143237141743</v>
+        <v>30.71647339022352</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2506,19 +2506,19 @@
         <v>117.5424354444279</v>
       </c>
       <c r="F56" t="n">
-        <v>30.61567908525337</v>
+        <v>30.37426565859309</v>
       </c>
       <c r="G56" t="n">
         <v>117.5424354444279</v>
       </c>
       <c r="H56" t="n">
-        <v>30.1019712935577</v>
+        <v>29.81811987714325</v>
       </c>
       <c r="I56" t="n">
         <v>83.79447116611811</v>
       </c>
       <c r="J56" t="n">
-        <v>30.70715611860922</v>
+        <v>29.81881279616872</v>
       </c>
       <c r="K56" t="n">
         <v>83.79447116611811</v>
@@ -2788,7 +2788,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>9.244753754725169</v>
+        <v>0</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2802,19 +2802,19 @@
         <v>117.5424354444279</v>
       </c>
       <c r="F64" t="n">
-        <v>9.292738133514664</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
         <v>117.5424354444279</v>
       </c>
       <c r="H64" t="n">
-        <v>9.283685917545093</v>
+        <v>0.2455248024228726</v>
       </c>
       <c r="I64" t="n">
         <v>117.5424354444279</v>
       </c>
       <c r="J64" t="n">
-        <v>9.283685917545098</v>
+        <v>0.2476153062220029</v>
       </c>
       <c r="K64" t="n">
         <v>117.5424354444279</v>
@@ -2825,7 +2825,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>18.64207447014618</v>
+        <v>4.574306568928062</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2839,19 +2839,19 @@
         <v>117.5424354444279</v>
       </c>
       <c r="F65" t="n">
-        <v>18.76582036238141</v>
+        <v>4.552207762511317</v>
       </c>
       <c r="G65" t="n">
         <v>117.5424354444279</v>
       </c>
       <c r="H65" t="n">
-        <v>18.65644543010609</v>
+        <v>4.568785458224852</v>
       </c>
       <c r="I65" t="n">
         <v>117.5424354444279</v>
       </c>
       <c r="J65" t="n">
-        <v>18.65422467734261</v>
+        <v>4.568315097408162</v>
       </c>
       <c r="K65" t="n">
         <v>117.5424354444279</v>
@@ -2862,7 +2862,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>18.78787393846795</v>
+        <v>4.574306568928062</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2876,19 +2876,19 @@
         <v>117.5424354444279</v>
       </c>
       <c r="F66" t="n">
-        <v>18.84418837454303</v>
+        <v>4.888746698613505</v>
       </c>
       <c r="G66" t="n">
         <v>117.5424354444279</v>
       </c>
       <c r="H66" t="n">
-        <v>19.26043880434065</v>
+        <v>5.47442276197163</v>
       </c>
       <c r="I66" t="n">
         <v>117.5424354444279</v>
       </c>
       <c r="J66" t="n">
-        <v>18.65525397928913</v>
+        <v>5.473259482129463</v>
       </c>
       <c r="K66" t="n">
         <v>117.5424354444279</v>
@@ -3107,13 +3107,13 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>4.682617809375553</v>
+        <v>117.5424354444279</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>4.682617809375553</v>
+        <v>117.5424354444279</v>
       </c>
     </row>
     <row r="73">
@@ -3144,13 +3144,13 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>8.020950673252573</v>
+        <v>117.5424354444279</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>8.020950673252573</v>
+        <v>117.5424354444279</v>
       </c>
     </row>
     <row r="74">
@@ -3181,13 +3181,13 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>10.65488636868937</v>
+        <v>117.5424354444279</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>10.65488636868937</v>
+        <v>117.5424354444279</v>
       </c>
     </row>
     <row r="75">
@@ -3218,13 +3218,13 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>12.84431593130606</v>
+        <v>117.5424354444279</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>12.84431593130606</v>
+        <v>117.5424354444279</v>
       </c>
     </row>
     <row r="76">
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>14.721932539954</v>
+        <v>117.5424354444279</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>14.721932539954</v>
+        <v>117.5424354444279</v>
       </c>
     </row>
     <row r="77">
@@ -3289,16 +3289,16 @@
         <v>117.5424354444279</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>1.03134314260017</v>
       </c>
       <c r="I77" t="n">
-        <v>4.682617809375553</v>
+        <v>117.5424354444279</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>4.682617809375553</v>
+        <v>117.5424354444279</v>
       </c>
     </row>
     <row r="78">
@@ -3326,16 +3326,16 @@
         <v>117.5424354444279</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>1.03134314260017</v>
       </c>
       <c r="I78" t="n">
-        <v>8.020950673252573</v>
+        <v>117.5424354444279</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>8.020950673252573</v>
+        <v>117.5424354444279</v>
       </c>
     </row>
     <row r="79">
@@ -3363,16 +3363,16 @@
         <v>117.5424354444279</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>1.03134314260017</v>
       </c>
       <c r="I79" t="n">
-        <v>10.65488636868937</v>
+        <v>117.5424354444279</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>10.65488636868937</v>
+        <v>117.5424354444279</v>
       </c>
     </row>
     <row r="80">
@@ -3403,13 +3403,13 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>12.84431593130606</v>
+        <v>117.5424354444279</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>12.84431593130606</v>
+        <v>117.5424354444279</v>
       </c>
     </row>
     <row r="81">
@@ -3440,13 +3440,13 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>14.721932539954</v>
+        <v>117.5424354444279</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>14.721932539954</v>
+        <v>117.5424354444279</v>
       </c>
     </row>
     <row r="82">
